--- a/Semiconductor/QUIK.xlsx
+++ b/Semiconductor/QUIK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameel/Library/CloudStorage/Dropbox/models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E78F111-AD5B-1449-929D-832EE2346AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF9E5E0-C281-5E41-805B-F6B798657A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5340" yWindow="4380" windowWidth="24320" windowHeight="24700" activeTab="1" xr2:uid="{CED5AF02-4096-2C42-A814-858C071FF889}"/>
+    <workbookView xWindow="12700" yWindow="1320" windowWidth="34220" windowHeight="24700" activeTab="1" xr2:uid="{CED5AF02-4096-2C42-A814-858C071FF889}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -385,8 +385,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -467,11 +467,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>5.62</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -895,10 +895,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="1">
-        <v>16.426947999999999</v>
+        <v>17.090253000000001</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -907,7 +907,7 @@
       </c>
       <c r="H5" s="1">
         <f>+H3*H4</f>
-        <v>92.319447760000003</v>
+        <v>116.89733052</v>
       </c>
     </row>
     <row r="6" spans="2:9">
@@ -915,11 +915,11 @@
         <v>3</v>
       </c>
       <c r="H6" s="1">
-        <v>19.190999999999999</v>
+        <v>17.343</v>
       </c>
       <c r="I6" s="1" t="str">
         <f>+I4</f>
-        <v>Q225</v>
+        <v>Q325</v>
       </c>
     </row>
     <row r="7" spans="2:9">
@@ -927,12 +927,12 @@
         <v>4</v>
       </c>
       <c r="H7" s="1">
-        <f>15+1.424+0.724</f>
-        <v>17.148</v>
+        <f>15+1.234</f>
+        <v>16.234000000000002</v>
       </c>
       <c r="I7" s="1" t="str">
         <f>+I6</f>
-        <v>Q225</v>
+        <v>Q325</v>
       </c>
     </row>
     <row r="8" spans="2:9">
@@ -944,7 +944,7 @@
       </c>
       <c r="H8" s="1">
         <f>+H5-H6+H7</f>
-        <v>90.276447759999996</v>
+        <v>115.78833051999999</v>
       </c>
     </row>
     <row r="10" spans="2:9">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="M4" s="11">
         <f>+M5-M3</f>
-        <v>900</v>
+        <v>929</v>
       </c>
     </row>
     <row r="5" spans="2:22" s="11" customFormat="1">
@@ -1207,11 +1207,10 @@
         <v>3687</v>
       </c>
       <c r="M5" s="11">
-        <f>AVERAGE(2000*0.9,2000*1.1)</f>
-        <v>2000</v>
+        <v>2029</v>
       </c>
       <c r="N5" s="11">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="R5" s="11">
         <v>12685</v>
@@ -1227,7 +1226,7 @@
       </c>
       <c r="V5" s="11">
         <f>SUM(K5:N5)</f>
-        <v>19012</v>
+        <v>16041</v>
       </c>
     </row>
     <row r="6" spans="2:22">
@@ -1244,7 +1243,7 @@
         <v>1537</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" ref="F6:F16" si="0">+T6-SUM(C6:E6)</f>
+        <f t="shared" ref="F6:F14" si="0">+T6-SUM(C6:E6)</f>
         <v>1713</v>
       </c>
       <c r="G6" s="1">
@@ -1753,27 +1752,27 @@
         <v>37</v>
       </c>
       <c r="G19" s="8">
-        <f>+G5/C5-1</f>
+        <f t="shared" ref="G19:L19" si="2">+G5/C5-1</f>
         <v>0.37164287442535682</v>
       </c>
       <c r="H19" s="8">
-        <f>+H5/D5-1</f>
+        <f t="shared" si="2"/>
         <v>0.41287230400547759</v>
       </c>
       <c r="I19" s="8">
-        <f>+I5/E5-1</f>
+        <f t="shared" si="2"/>
         <v>-0.35888972243060768</v>
       </c>
       <c r="J19" s="8">
-        <f>+J5/F5-1</f>
+        <f t="shared" si="2"/>
         <v>-0.19200427864687797</v>
       </c>
       <c r="K19" s="8">
-        <f>+K5/G5-1</f>
+        <f t="shared" si="2"/>
         <v>-0.23707884988534134</v>
       </c>
       <c r="L19" s="8">
-        <f>+L5/H5-1</f>
+        <f t="shared" si="2"/>
         <v>-0.10661497455779012</v>
       </c>
       <c r="S19" s="8">
@@ -1798,27 +1797,27 @@
         <v>0.57827244132591338</v>
       </c>
       <c r="D20" s="7">
-        <f t="shared" ref="D20:J20" si="2">(D5-D6) / D5</f>
+        <f t="shared" ref="D20:I20" si="3">(D5-D6) / D5</f>
         <v>0.41184525847312564</v>
       </c>
       <c r="E20" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.76939234808702173</v>
       </c>
       <c r="F20" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.77095868431608505</v>
       </c>
       <c r="G20" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.76697830305168457</v>
       </c>
       <c r="H20" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.51005573055488251</v>
       </c>
       <c r="I20" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.55815586239176218</v>
       </c>
       <c r="J20" s="7">
@@ -1826,23 +1825,23 @@
         <v>0.50438523911964261</v>
       </c>
       <c r="K20" s="7">
-        <f t="shared" ref="K20:L20" si="3">(K5-K6) / K5</f>
+        <f t="shared" ref="K20:L20" si="4">(K5-K6) / K5</f>
         <v>0.43398843930635839</v>
       </c>
       <c r="L20" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.25874694873881204</v>
       </c>
       <c r="R20" s="7">
-        <f t="shared" ref="R20:T20" si="4">(R5-R6) / R5</f>
+        <f t="shared" ref="R20:T20" si="5">(R5-R6) / R5</f>
         <v>0.58486401261332277</v>
       </c>
       <c r="S20" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.54400494437577251</v>
       </c>
       <c r="T20" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.68341352957826207</v>
       </c>
     </row>
@@ -1852,7 +1851,7 @@
       </c>
       <c r="V22" s="1">
         <f>+Main!H8</f>
-        <v>90.276447759999996</v>
+        <v>115.78833051999999</v>
       </c>
     </row>
     <row r="23" spans="2:22" s="6" customFormat="1">
@@ -1869,7 +1868,7 @@
       </c>
       <c r="V23" s="13">
         <f>+$V$22/(20.112)</f>
-        <v>4.4886857478122515</v>
+        <v>5.757176338504375</v>
       </c>
     </row>
     <row r="24" spans="2:22">
@@ -1893,7 +1892,7 @@
       </c>
       <c r="V24" s="14">
         <f>(SUM(K5:N5)*V23)/10^3</f>
-        <v>85.338893437406526</v>
+        <v>92.350865645948687</v>
       </c>
     </row>
     <row r="25" spans="2:22">
@@ -1911,7 +1910,7 @@
       </c>
       <c r="V25" s="3">
         <f>+Main!H6</f>
-        <v>19.190999999999999</v>
+        <v>17.343</v>
       </c>
     </row>
     <row r="26" spans="2:22">
@@ -1929,7 +1928,7 @@
       </c>
       <c r="V26" s="1">
         <f>+Main!H7</f>
-        <v>17.148</v>
+        <v>16.234000000000002</v>
       </c>
     </row>
     <row r="27" spans="2:22">
@@ -1944,7 +1943,7 @@
       </c>
       <c r="V27" s="16">
         <f>+V24+V25-V26</f>
-        <v>87.381893437406532</v>
+        <v>93.459865645948696</v>
       </c>
     </row>
     <row r="28" spans="2:22">
@@ -1962,7 +1961,7 @@
       </c>
       <c r="V28" s="1">
         <f>+Main!H4</f>
-        <v>16.426947999999999</v>
+        <v>17.090253000000001</v>
       </c>
     </row>
     <row r="29" spans="2:22">
@@ -1980,7 +1979,7 @@
       </c>
       <c r="V29" s="12">
         <f>+V27/V28</f>
-        <v>5.3194235129621479</v>
+        <v>5.4686063246663865</v>
       </c>
     </row>
     <row r="30" spans="2:22">
@@ -1998,7 +1997,7 @@
       </c>
       <c r="V30" s="7">
         <f>+V29/V33-1</f>
-        <v>-5.3483360682891834E-2</v>
+        <v>-0.20049615136456334</v>
       </c>
     </row>
     <row r="31" spans="2:22">
@@ -2038,7 +2037,7 @@
       </c>
       <c r="V33" s="15">
         <f>+Main!H3</f>
-        <v>5.62</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="34" spans="2:22">
